--- a/app/content/fuma.xlsx
+++ b/app/content/fuma.xlsx
@@ -1549,7 +1549,7 @@
         <v>官威压顶</v>
       </c>
       <c r="C2" t="str">
-        <v>威</v>
+        <v>势</v>
       </c>
       <c r="D2" t="str">
         <v>抬出大理寺与圣旨限期，教他不敢造次。</v>
@@ -1572,7 +1572,7 @@
         <v>亮出铁证</v>
       </c>
       <c r="C3" t="str">
-        <v>威</v>
+        <v>器</v>
       </c>
       <c r="D3" t="str">
         <v>将物证拍在案上，以实据夺人。</v>
@@ -1583,8 +1583,8 @@
       <c r="F3">
         <v>4</v>
       </c>
-      <c r="G3">
-        <v>3</v>
+      <c r="G3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -1595,7 +1595,7 @@
         <v>银钱开路</v>
       </c>
       <c r="C4" t="str">
-        <v>利</v>
+        <v>器</v>
       </c>
       <c r="D4" t="str">
         <v>许以好处，买一句真话。</v>
@@ -1618,7 +1618,7 @@
         <v>抬出靠山</v>
       </c>
       <c r="C5" t="str">
-        <v>利</v>
+        <v>势</v>
       </c>
       <c r="D5" t="str">
         <v>点破他背后的人，教他掂量轻重。</v>
@@ -1629,8 +1629,8 @@
       <c r="F5">
         <v>2</v>
       </c>
-      <c r="G5">
-        <v>1</v>
+      <c r="G5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1641,7 +1641,7 @@
         <v>将心比心</v>
       </c>
       <c r="C6" t="str">
-        <v>情</v>
+        <v>策</v>
       </c>
       <c r="D6" t="str">
         <v>说一句市井小民的难处，松他的口风。</v>
@@ -1652,8 +1652,8 @@
       <c r="F6">
         <v>2</v>
       </c>
-      <c r="G6">
-        <v>1</v>
+      <c r="G6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1664,7 +1664,7 @@
         <v>诉之亲情</v>
       </c>
       <c r="C7" t="str">
-        <v>情</v>
+        <v>隐</v>
       </c>
       <c r="D7" t="str">
         <v>问他家中妻小，唤他的怕与悔。</v>
@@ -1687,7 +1687,7 @@
         <v>条分缕析</v>
       </c>
       <c r="C8" t="str">
-        <v>理</v>
+        <v>策</v>
       </c>
       <c r="D8" t="str">
         <v>把案情掰开揉碎，讲给他自己听。</v>
@@ -1710,7 +1710,7 @@
         <v>晓明律法</v>
       </c>
       <c r="C9" t="str">
-        <v>理</v>
+        <v>策</v>
       </c>
       <c r="D9" t="str">
         <v>讲清知情不举与从犯的分别，给他指一条活路。</v>
@@ -1721,8 +1721,8 @@
       <c r="F9">
         <v>4</v>
       </c>
-      <c r="G9">
-        <v>3</v>
+      <c r="G9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1732,6 +1732,9 @@
       <c r="B10" t="str">
         <v>太皇太后密信</v>
       </c>
+      <c r="C10" t="str">
+        <v>器</v>
+      </c>
       <c r="D10" t="str">
         <v>对局中亮出：黄锦封皮，亲笔手书——任何人见了都要跪。</v>
       </c>
@@ -1752,6 +1755,9 @@
       <c r="B11" t="str">
         <v>龙凤玉珏</v>
       </c>
+      <c r="C11" t="str">
+        <v>器</v>
+      </c>
       <c r="D11" t="str">
         <v>对局中出示：御赐之物，见珏如见公主。</v>
       </c>
@@ -1772,6 +1778,9 @@
       <c r="B12" t="str">
         <v>无指纹的短匕</v>
       </c>
+      <c r="C12" t="str">
+        <v>器</v>
+      </c>
       <c r="D12" t="str">
         <v>对局中掷出：刀柄无掌纹的凶器，一掷便破一切伪装。</v>
       </c>
@@ -1792,6 +1801,9 @@
       <c r="B13" t="str">
         <v>翻倒的烛台</v>
       </c>
+      <c r="C13" t="str">
+        <v>器</v>
+      </c>
       <c r="D13" t="str">
         <v>对局中出示：新旧交错的灼痕，最有力的开场白。</v>
       </c>
@@ -1812,6 +1824,9 @@
       <c r="B14" t="str">
         <v>《无欲则刚》拓片</v>
       </c>
+      <c r="C14" t="str">
+        <v>器</v>
+      </c>
       <c r="D14" t="str">
         <v>对局中使用：先父手书四字，抚之可定心神。（+3）</v>
       </c>
@@ -1832,6 +1847,9 @@
       <c r="B15" t="str">
         <v>十万两银票</v>
       </c>
+      <c r="C15" t="str">
+        <v>器</v>
+      </c>
       <c r="D15" t="str">
         <v>对局中使用：内廷行贿铁证在手，下一言掷地有声。（成术+3）</v>
       </c>
@@ -1852,8 +1870,11 @@
       <c r="B16" t="str">
         <v>诚仆李三</v>
       </c>
+      <c r="C16" t="str">
+        <v>势</v>
+      </c>
       <c r="D16" t="str">
-        <v>携带：情牌 +1。那个替主家守了二十年秘密的老实人。</v>
+        <v>携带：策牌 +1。那个替主家守了二十年秘密的老实人。</v>
       </c>
       <c r="E16" t="str">
         <v>「小的看得真切。」——他这一生，就真切过这一回。</v>
@@ -1872,8 +1893,11 @@
       <c r="B17" t="str">
         <v>同窗张彦</v>
       </c>
+      <c r="C17" t="str">
+        <v>势</v>
+      </c>
       <c r="D17" t="str">
-        <v>携带：理牌 +1。驸马的同窗，最先冲上二楼的人。</v>
+        <v>携带：隐牌 +1。驸马的同窗，最先冲上二楼的人。</v>
       </c>
       <c r="E17" t="str">
         <v>他到现在还记得那声巨响。也记得门缝里的血。</v>
@@ -1892,8 +1916,11 @@
       <c r="B18" t="str">
         <v>行商周奎</v>
       </c>
+      <c r="C18" t="str">
+        <v>势</v>
+      </c>
       <c r="D18" t="str">
-        <v>携带：利牌 +1。见过赵作最后清醒时刻的送酒人。</v>
+        <v>携带：器牌 +1。见过赵作最后清醒时刻的送酒人。</v>
       </c>
       <c r="E18" t="str">
         <v>他后来再没进过金陵城的酒楼。</v>
@@ -1912,8 +1939,11 @@
       <c r="B19" t="str">
         <v>主事沈砚</v>
       </c>
+      <c r="C19" t="str">
+        <v>势</v>
+      </c>
       <c r="D19" t="str">
-        <v>携带：威牌 +1，气力上限 +2。年少刚正，不通权术。</v>
+        <v>携带：势牌 +1，气力上限 +2。年少刚正，不通权术。</v>
       </c>
       <c r="E19" t="str">
         <v>满朝都说他傻。你在卷宗末页写：可用。</v>
@@ -1932,6 +1962,9 @@
       <c r="B20" t="str">
         <v>店主王满财</v>
       </c>
+      <c r="C20" t="str">
+        <v>势</v>
+      </c>
       <c r="D20" t="str">
         <v>携带：气力上限 +2。改了口供又被你掰回来的圆滑人。</v>
       </c>
@@ -1952,6 +1985,9 @@
       <c r="B21" t="str">
         <v>纹银十两</v>
       </c>
+      <c r="C21" t="str">
+        <v>器</v>
+      </c>
       <c r="D21" t="str">
         <v>资源卡：翻到即入钱袋。</v>
       </c>
@@ -1971,6 +2007,9 @@
       </c>
       <c r="B22" t="str">
         <v>官银三十两</v>
+      </c>
+      <c r="C22" t="str">
+        <v>器</v>
       </c>
       <c r="D22" t="str">
         <v>资源卡：翻到即入钱袋。</v>
@@ -2205,7 +2244,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>利,威,利,情,威,情,理</v>
+        <v>策,势,策,隐,势,策,策</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -2237,7 +2276,7 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>10/10</v>
+        <v>10/8</v>
       </c>
       <c r="H3" t="str">
         <v>p_shen_1,p_shen_2,p_shen_3,p_shen_1,p_shen_3</v>
